--- a/Result/profitability/2355.xlsx
+++ b/Result/profitability/2355.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.26</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4575</v>
+        <v>0.43125</v>
       </c>
       <c r="N2" t="n">
-        <v>12.41875</v>
+        <v>12.03875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.57</v>
       </c>
       <c r="M3" t="n">
-        <v>0.44625</v>
+        <v>0.4375</v>
       </c>
       <c r="N3" t="n">
-        <v>12.2275</v>
+        <v>12.295</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.54</v>
       </c>
       <c r="M4" t="n">
-        <v>0.44875</v>
+        <v>0.4400000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>12.4575</v>
+        <v>12.4075</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.24</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4137500000000001</v>
+        <v>0.43875</v>
       </c>
       <c r="N5" t="n">
-        <v>12.42375</v>
+        <v>12.59125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.31</v>
       </c>
       <c r="M6" t="n">
-        <v>0.42125</v>
+        <v>0.45375</v>
       </c>
       <c r="N6" t="n">
-        <v>13.2375</v>
+        <v>13.68625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.61</v>
       </c>
       <c r="M7" t="n">
-        <v>0.47375</v>
+        <v>0.45</v>
       </c>
       <c r="N7" t="n">
-        <v>14.05625</v>
+        <v>13.8325</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.79</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4925</v>
+        <v>0.47125</v>
       </c>
       <c r="N8" t="n">
-        <v>14.625</v>
+        <v>14.6375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.74</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5075000000000001</v>
+        <v>0.5075</v>
       </c>
       <c r="N9" t="n">
         <v>15.22875</v>
@@ -1772,7 +1772,7 @@
         <v>0.89</v>
       </c>
       <c r="M11" t="n">
-        <v>0.56625</v>
+        <v>0.5662499999999999</v>
       </c>
       <c r="N11" t="n">
         <v>15.24625</v>
@@ -2026,7 +2026,7 @@
         <v>0.31</v>
       </c>
       <c r="M13" t="n">
-        <v>0.62</v>
+        <v>0.6200000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>15.495</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4241</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3725</v>
+      </c>
+      <c r="E75" t="n">
+        <v>517</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="G75" t="n">
+        <v>187</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.41%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>99</v>
+      </c>
+      <c r="J75" t="n">
+        <v>286</v>
+      </c>
+      <c r="K75" t="n">
+        <v>180</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.1375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2741935483870968</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.008278145695364225</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1236162361623616</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
